--- a/tools/proef-armaturen.xlsx
+++ b/tools/proef-armaturen.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armaturenlijst" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notities" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -414,50 +414,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Armaturenlijst - Proefproject</t>
+          <t>Armatuurcode</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Aantallen</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leverancier / merk / type </t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Voorbeeld</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ARTIKELCODE</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>OMSCRHIJVING</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>VOORBEELD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>OPMERKINGEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KANTOOR</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>HAL</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aantal</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Merk</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ruimte</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Artikelnummer</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Omschrijving</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Opmerking</t>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TOTAAL</t>
         </is>
       </c>
     </row>
@@ -470,14 +502,12 @@
       <c r="B4" t="n">
         <v>12</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pragmalux</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Kantoor</t>
+      <c r="F4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bestekarmatuur X</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -498,6 +528,9 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1084459-SN</t>
@@ -506,6 +539,11 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>Pragmalux LED Plafonnière / Wandarmatuur Dura-M Wit Ø340 IP64 IK10 8-18W 750-2075lm 2200K-2700K 2-CCT + bewegingssensor + noodmodule 3uur autotest</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Niet IK10</t>
         </is>
       </c>
     </row>
@@ -515,6 +553,12 @@
           <t>C</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>9999999</t>
@@ -525,7 +569,7 @@
           <t>Eigen armatuur &amp; zo</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>via de leverancier</t>
         </is>
@@ -548,6 +592,9 @@
         <is>
           <t>Gang</t>
         </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -607,7 +654,125 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1000947-OS + 1000282</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Pragmalux LED Paneel 30x120cm Sigma G2 IP44 18-26W 3000K-4000K 2-CCT 2400-3650lm UGR&lt;19 +Osram Driver (2x28W) + Pragmalux Noodmodule Kit t.b.v. Panelen &amp; Downlights 3 uur met autotest</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>WS1046761 + 9322219-300 + 1000282</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Pragmalux LED Downlight Essence G2 IP54 wit standaard max. 15W 3000K-6000K 3-CCT max. 1650lm 100D Ø200 Buitenmaat - Gatmaat Ø150 excl. LED Driver + Philips Driver Xitanium 20W/m 300mA 44V DS I 230V incl. DC kabel + Pragmalux Noodmodule Kit t.b.v. Panelen &amp; Downlights 3 uur met autotest</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1084459-S+1047515</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Pragmalux LED Plafonnière / Wandarmatuur Dura-M Wit Ø340 IP64 IK10 8-18W 750-2075lm 2200K-2700K 2-CCT + bewegingssensor + Pragmalux LED Inbouw/Opbouw Downlight Luna G2 IP44 12W/18W 3000K-6000K 3-CCT 1400-2050lm Ø217 Buitenmaat - Gatmaat Ø65-185 incl. LED Driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Special</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>DLC - volledige eigen naam special</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
